--- a/docs/package/05_Delivery/Upload_Templates/Credit_Life_Members_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Credit_Life_Members_Upload_Template.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">birthDate, birth date, birthday, date of birth</t>
   </si>
   <si>
-    <t xml:space="preserve">Text 30; one active certificate per loan account</t>
+    <t xml:space="preserve">TFS loan number, 10 digits (credit_life.loan_account_pattern); one active certificate per loan account</t>
   </si>
   <si>
     <t xml:space="preserve">loanAccount, loan account, tfs loan account</t>

--- a/docs/package/05_Delivery/Upload_Templates/Credit_Life_Members_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Credit_Life_Members_Upload_Template.xlsx
@@ -231,7 +231,7 @@
     <t xml:space="preserve">Upload on</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Credit Life &gt; Batch &gt; Upload Members</t>
+    <t xml:space="preserve">Policy Servicing &gt; Credit Life &gt; Batch &gt; Upload Members</t>
   </si>
   <si>
     <t xml:space="preserve">File types</t>
